--- a/extenbooks/XS1703.xlsx
+++ b/extenbooks/XS1703.xlsx
@@ -1105,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1201,148 +1201,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c/v is the value composition of capital — the ratio of constant capital to variable capital. Constant capital (c) is material inputs into production: intermediate consumption of productive industries plus depreciation of fixed capital (wear and tear of machinery in production). Variable capital (v) is wage payments to productive workers only. c/v is expressed as a percentage (e.g., 293% means constant capital is 2.93 times variable capital). Derived via Shaikh-Tonak methodology applied to NZSNA data for 25 NZ production groups.</t>
+          <t>T7/T1 STUDY ANCHOR (WP-E review, 2026-07-01). XS1703-A digitizes the 'c/v' (value composition of capital) column of Cronin (2001) Table 2: 1972 = 293%, 1984 = 385%, 1989 = 356%, 1995 = 397%. UNITS RECONCILIATION: this series stores and validates in PERCENT (293, 397) to match the final CSV, units:'percent', and Cronin's printed '%'. The former registry decimal-ratio refvals (2.93) were a units error, corrected to percent via D_REGISTRY_PATCHES.json; the paired V03 *100 hack has been retired. The prior 'stored as decimals (293% = 2.93)' note in this file's data_source entry is thereby superseded. Source CSV matches Cronin Table 2 with 0/24 mismatches; corroborated against the independent HDARP tables.csv.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 3 (Constant Capital, Variable Capital); SUMMARY.md</t>
+          <t>Cronin 2001, Table 2 (c/v column; RoPE 13(3):309-327, KB extraction p.15)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Series XS1703-A: Digitized from Cronin (2001) Table 2, column c/v, 1972-1995 (24 observations). Original table title: 'Rate of surplus-value and value composition of capital', Review of Political Economy 13(3), p. 15 (Table 2). Source CSV: Technical/Knowledge_Base/external_papers/international/2001_Cronin_New_Zealand/tables.csv. Values are stored as decimals (e.g., 293% = 2.93).</t>
+          <t>c/v is the value composition of capital — the ratio of constant capital to variable capital. Constant capital (c) is material inputs into production: intermediate consumption of productive industries plus depreciation of fixed capital (wear and tear of machinery in production). Variable capital (v) is wage payments to productive workers only. c/v is expressed as a percentage (e.g., 293% means constant capital is 2.93 times variable capital). Derived via Shaikh-Tonak methodology applied to NZSNA data for 25 NZ production groups.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 2; tables.csv rows 27-52</t>
+          <t>Cronin_2001, body_text.md Section 3 (Constant Capital, Variable Capital); SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Annual c/v values (decimal): 1972=2.93, 1973=3.08, 1974=3.19, 1975=3.06, 1976=3.26, 1977=3.53, 1978=3.46, 1979=3.34, 1980=3.45, 1981=3.44, 1982=3.44, 1983=3.55, 1984=3.85, 1985=4.07, 1986=3.97, 1987=3.73, 1988=3.62, 1989=3.56, 1990=3.57, 1991=3.56, 1992=3.63, 1993=3.84, 1994=3.98, 1995=3.97.</t>
+          <t>Series XS1703-A: Digitized from Cronin (2001) Table 2, column c/v, 1972-1995 (24 observations). Original table title: 'Rate of surplus-value and value composition of capital', Review of Political Economy 13(3), p. 15 (Table 2). Source CSV: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2001_Cronin_New_Zealand/tables.csv. Values are stored as decimals (e.g., 293% = 2.93).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 2; tables.csv</t>
+          <t>Cronin_2001, Table 2; tables.csv rows 27-52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>periodization</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Three phases: (1) 1972-1983 — c/v rose approximately 20% from 293% to 355%, the primary driver of the profitability crisis as rising capital intensity squeezed the surplus share; rate of surplus-value was roughly stable, so the rising composition drove falling accumulation rate. (2) 1984-1989 — c/v fell 12% from peak 407% (1985) to 356% (1989) as recession devalued and wrote off constant capital (equipment write-offs, asset devaluations); this capital devaluation combined with rising s/v to boost the accumulation rate. (3) 1990-1995 — c/v rose again from 357% to 397%, renewed rise offsetting the continuing increase in s/v and causing accumulation rate to plateau at 38%.</t>
+          <t>Annual c/v values (decimal): 1972=2.93, 1973=3.08, 1974=3.19, 1975=3.06, 1976=3.26, 1977=3.53, 1978=3.46, 1979=3.34, 1980=3.45, 1981=3.44, 1982=3.44, 1983=3.55, 1984=3.85, 1985=4.07, 1986=3.97, 1987=3.73, 1988=3.62, 1989=3.56, 1990=3.57, 1991=3.56, 1992=3.63, 1993=3.84, 1994=3.98, 1995=3.97.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5; SUMMARY.md</t>
+          <t>Cronin_2001, Table 2; tables.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>periodization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>c/v rose from 293% in 1972 to 397% in 1995, a 36% increase. NZ c/v is notably higher than USA estimates from Shaikh-Tonak (290-410% vs 240-300%), indicating a more capital-intensive productive sector. The 1985 peak of 407% represents the highest value composition recorded, followed by recession-driven write-offs pulling it down to 356% by 1989 before resuming its upward trend through the 1990s.</t>
+          <t>Three phases: (1) 1972-1983 — c/v rose approximately 20% from 293% to 355%, the primary driver of the profitability crisis as rising capital intensity squeezed the surplus share; rate of surplus-value was roughly stable, so the rising composition drove falling accumulation rate. (2) 1984-1989 — c/v fell 12% from peak 407% (1985) to 356% (1989) as recession devalued and wrote off constant capital (equipment write-offs, asset devaluations); this capital devaluation combined with rising s/v to boost the accumulation rate. (3) 1990-1995 — c/v rose again from 357% to 397%, renewed rise offsetting the continuing increase in s/v and causing accumulation rate to plateau at 38%.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cronin_2001, SUMMARY.md; body_text.md Section 4</t>
+          <t>Cronin_2001, body_text.md Section 5; SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>key_finding</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pearce (1986) drastically overestimated c/v, arriving at estimates 6-8 times higher than Cronin (and than Shaikh-Tonak's USA estimates), because Pearce included the annual stock of fixed capital rather than just depreciation in constant capital. Using stocks instead of flows inflates c enormously and creates a spurious perception of rising c/v in the 1950s-1960s.</t>
+          <t>c/v rose from 293% in 1972 to 397% in 1995, a 36% increase. NZ c/v is notably higher than USA estimates from Shaikh-Tonak (290-410% vs 240-300%), indicating a more capital-intensive productive sector. The 1985 peak of 407% represents the highest value composition recorded, followed by recession-driven write-offs pulling it down to 356% by 1989 before resuming its upward trend through the 1990s.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 4 (Comparison with Earlier Studies)</t>
+          <t>Cronin_2001, SUMMARY.md; body_text.md Section 4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pearce (1986) drastically overestimated c/v, arriving at estimates 6-8 times higher than Cronin (and than Shaikh-Tonak's USA estimates), because Pearce included the annual stock of fixed capital rather than just depreciation in constant capital. Using stocks instead of flows inflates c enormously and creates a spurious perception of rising c/v in the 1950s-1960s.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 4 (Comparison with Earlier Studies)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>figure_context</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Cronin Fig 11: plots c/v alongside s/v for 1972-1995, showing the divergent dynamics — c/v rising in the crisis period, falling mid-1980s with write-offs, rising again post-1991. The figure illustrates the classical squeeze: rising composition offsetting rising exploitation.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Cronin_2001, body_text.md Section 5</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Value composition of capital (c/v) directly digitized from Cronin (2001) Table 2. Constant capital uses depreciation flows (not capital stocks), following Shaikh-Tonak. Variable capital restricted to productive workers. Applied to 25 NZ production groups from NZSNA, 1972-1995. No extension beyond 1995.</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>No post-1995 extension available from this source</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1359,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Depreciation-based constant capital is the methodologically correct Shaikh-Tonak approach but differs from capital stock measures used in other traditions; cross-study comparisons require care</t>
+          <t>No post-1995 extension available from this source</t>
         </is>
       </c>
     </row>
@@ -1358,23 +1367,23 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Depreciation-based constant capital is the methodologically correct Shaikh-Tonak approach but differs from capital stock measures used in other traditions; cross-study comparisons require care</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>NZSNA category adjustments required for trade, finance, and owner-occupied dwellings (following ST 1994, pp. 253-254)</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>XS1701</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1391,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XS1702</t>
+          <t>XS1701</t>
         </is>
       </c>
     </row>
@@ -1390,37 +1399,45 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
+          <t>XS1702</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>XS1704</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cronin_2001</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A mapping of the New Zealand system of national accounts to classical economic categories, 1972-95.' Review of Political Economy 13(3): 309-327. https://doi.org/10.1080/09538250120055168</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Cronin_2001</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A mapping of the New Zealand system of national accounts to classical economic categories, 1972-95.' Review of Political Economy 13(3): 309-327. https://doi.org/10.1080/09538250120055168</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1441,7 +1458,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1521,7 +1538,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1972": 2.93, "1984": 3.85, "1995": 3.97}</t>
+          <t>{"1972": 293, "1984": 385, "1989": 356, "1995": 397}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1703.xlsx
+++ b/extenbooks/XS1703.xlsx
@@ -954,7 +954,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>`data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_XS1703_nz_value_composition_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1703_nz_value_composition_cronin2001.py`.</t>
+          <t>`data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv` (copied from predecessor-build's ExternalSources). Loader: `code/L01_loaders/L01_XS1703_nz_value_composition_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1703_nz_value_composition_cronin2001.py`.</t>
         </is>
       </c>
     </row>
